--- a/api/templates/export/device_operation_logs/es.xlsx
+++ b/api/templates/export/device_operation_logs/es.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\export\contacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\export\device_operation_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A57C2A6-CEE3-40E9-8D7B-CEB9A7EA2315}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0C3D7A-9D06-424F-99F2-4C4B0E993486}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="20734" windowHeight="11760" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="480" windowWidth="20730" windowHeight="11760" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
   <si>
     <t>Code</t>
   </si>
@@ -127,43 +127,73 @@
     <t>Signal loss detected in the amplification curve</t>
   </si>
   <si>
-    <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;level&gt;</t>
-  </si>
-  <si>
-    <t>&lt;state&gt;</t>
-  </si>
-  <si>
-    <t>&lt;lga&gt;</t>
-  </si>
-  <si>
-    <t>&lt;tags&gt;</t>
-  </si>
-  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>Contactos Aspect</t>
-  </si>
-  <si>
-    <t>Impreso: &lt;date&gt;</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Funcion</t>
-  </si>
-  <si>
-    <t>Estado/Provincia</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Etiquetas</t>
+    <t>&lt;createdOn&gt;</t>
+  </si>
+  <si>
+    <t>&lt;logLevel&gt;</t>
+  </si>
+  <si>
+    <t>&lt;logType&gt;</t>
+  </si>
+  <si>
+    <t>&lt;calibrationMessage&gt;</t>
+  </si>
+  <si>
+    <t>&lt;errorMessage&gt;</t>
+  </si>
+  <si>
+    <t>&lt;temperature&gt;</t>
+  </si>
+  <si>
+    <t>&lt;voltage&gt;</t>
+  </si>
+  <si>
+    <t>&lt;logText&gt;</t>
+  </si>
+  <si>
+    <t>&lt;logDetails&gt;</t>
+  </si>
+  <si>
+    <t>Log de operación de dispositívo</t>
+  </si>
+  <si>
+    <t>Dia de impresion: &lt;date&gt;</t>
+  </si>
+  <si>
+    <t>Dispositívo: &lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>Sitio: &lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Nivel de Log</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Mensaje de calibración</t>
+  </si>
+  <si>
+    <t>Mensaje de error</t>
+  </si>
+  <si>
+    <t>Temperatura</t>
+  </si>
+  <si>
+    <t>Volts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto </t>
+  </si>
+  <si>
+    <t>Detalles</t>
   </si>
 </sst>
 </file>
@@ -190,14 +220,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
@@ -214,8 +236,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -307,48 +337,48 @@
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -371,13 +401,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -388,6 +412,12 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -798,70 +828,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="33.2109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="53.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="33.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="34.1640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="8" max="8" width="65.58203125" customWidth="1"/>
+    <col min="9" max="9" width="47.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="31" x14ac:dyDescent="0.7">
+      <c r="A1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:5" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
+      <c r="H8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="I8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -877,14 +947,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.2109375" customWidth="1"/>
-    <col min="3" max="3" width="100.640625" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.25" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -895,7 +965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1001</v>
       </c>
@@ -906,7 +976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>1002</v>
       </c>
@@ -917,7 +987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>1004</v>
       </c>
@@ -928,7 +998,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>1005</v>
       </c>
@@ -939,7 +1009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>1006</v>
       </c>
@@ -950,7 +1020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>1007</v>
       </c>
@@ -961,7 +1031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>1017</v>
       </c>
@@ -972,7 +1042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>1018</v>
       </c>
@@ -983,7 +1053,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>2003</v>
       </c>
@@ -994,7 +1064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>2005</v>
       </c>
@@ -1005,7 +1075,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>2008</v>
       </c>
@@ -1016,7 +1086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>2009</v>
       </c>
@@ -1027,7 +1097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>2011</v>
       </c>
@@ -1038,7 +1108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>2014</v>
       </c>
@@ -1049,7 +1119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>2016</v>
       </c>
@@ -1060,7 +1130,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>2018</v>
       </c>
@@ -1071,7 +1141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>2022</v>
       </c>
@@ -1082,7 +1152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>2025</v>
       </c>
@@ -1093,7 +1163,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>2032</v>
       </c>
@@ -1104,7 +1174,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>2034</v>
       </c>
@@ -1115,7 +1185,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>2037</v>
       </c>
@@ -1126,7 +1196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>4010</v>
       </c>
@@ -1137,7 +1207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>4017</v>
       </c>
@@ -1148,7 +1218,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>5006</v>
       </c>
@@ -1159,7 +1229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>5007</v>
       </c>
@@ -1170,7 +1240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>5011</v>
       </c>

--- a/api/templates/export/device_operation_logs/es.xlsx
+++ b/api/templates/export/device_operation_logs/es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\export\device_operation_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0C3D7A-9D06-424F-99F2-4C4B0E993486}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531B5F54-7789-45ED-96F0-EE266217919F}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="480" windowWidth="20730" windowHeight="11760" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
   <si>
     <t>Code</t>
   </si>
@@ -139,21 +139,6 @@
     <t>&lt;logType&gt;</t>
   </si>
   <si>
-    <t>&lt;calibrationMessage&gt;</t>
-  </si>
-  <si>
-    <t>&lt;errorMessage&gt;</t>
-  </si>
-  <si>
-    <t>&lt;temperature&gt;</t>
-  </si>
-  <si>
-    <t>&lt;voltage&gt;</t>
-  </si>
-  <si>
-    <t>&lt;logText&gt;</t>
-  </si>
-  <si>
     <t>&lt;logDetails&gt;</t>
   </si>
   <si>
@@ -169,31 +154,22 @@
     <t>Sitio: &lt;siteName&gt;</t>
   </si>
   <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Nivel de Log</t>
-  </si>
-  <si>
     <t>Tipo</t>
   </si>
   <si>
-    <t>Mensaje de calibración</t>
-  </si>
-  <si>
-    <t>Mensaje de error</t>
-  </si>
-  <si>
-    <t>Temperatura</t>
-  </si>
-  <si>
-    <t>Volts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texto </t>
-  </si>
-  <si>
     <t>Detalles</t>
+  </si>
+  <si>
+    <t>Created On</t>
+  </si>
+  <si>
+    <t>&lt;message&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel de Log </t>
+  </si>
+  <si>
+    <t>Mensaje</t>
   </si>
 </sst>
 </file>
@@ -380,7 +356,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -394,9 +370,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -417,6 +390,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -828,109 +807,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.6640625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="33.25" style="3" customWidth="1"/>
     <col min="3" max="3" width="26.1640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="26" style="3" customWidth="1"/>
-    <col min="5" max="5" width="34.1640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="8" max="8" width="65.58203125" customWidth="1"/>
-    <col min="9" max="9" width="47.08203125" customWidth="1"/>
+    <col min="4" max="4" width="113.5" customWidth="1"/>
+    <col min="5" max="5" width="118.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31" x14ac:dyDescent="0.7">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" ht="31" x14ac:dyDescent="0.7">
+      <c r="A1" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="7" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="7" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="12" t="s">
+    </row>
+    <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
